--- a/research/traditional_assets/database/data/bermuda/bermuda_metals_mining.xlsx
+++ b/research/traditional_assets/database/data/bermuda/bermuda_metals_mining.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="K2">
-        <v>-0.967</v>
+        <v>-0.921</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -612,61 +612,67 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>2.07</v>
+        <v>0.373</v>
       </c>
       <c r="V2">
-        <v>0.2165271966527196</v>
+        <v>0.02207100591715977</v>
       </c>
       <c r="W2">
-        <v>-6.320261437908496</v>
+        <v>-0.2285359801488834</v>
       </c>
       <c r="X2">
-        <v>0.0640769953380476</v>
+        <v>0.1226965148274022</v>
       </c>
       <c r="Y2">
-        <v>-6.384338433246544</v>
+        <v>-0.3512324949762856</v>
       </c>
       <c r="Z2">
         <v>0</v>
       </c>
       <c r="AA2">
-        <v>-18.57692307692308</v>
+        <v>-0.4566326530612244</v>
       </c>
       <c r="AB2">
-        <v>0.0640769953380476</v>
+        <v>0.121543332350794</v>
       </c>
       <c r="AC2">
-        <v>-18.64100007226113</v>
+        <v>-0.5781759854120184</v>
       </c>
       <c r="AD2">
-        <v>0</v>
+        <v>0.372</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>0</v>
+        <v>0.372</v>
       </c>
       <c r="AG2">
-        <v>-2.07</v>
+        <v>-0.001000000000000001</v>
       </c>
       <c r="AH2">
-        <v>0</v>
+        <v>0.02153774895785086</v>
       </c>
       <c r="AI2">
-        <v>0</v>
+        <v>0.07894736842105264</v>
       </c>
       <c r="AJ2">
-        <v>-0.2763684913217623</v>
+        <v>-5.917509911829108e-05</v>
       </c>
       <c r="AK2">
-        <v>-0.7064846416382251</v>
+        <v>-0.0002304678497349622</v>
       </c>
       <c r="AL2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="AM2">
-        <v>0</v>
+        <v>0.01</v>
+      </c>
+      <c r="AO2">
+        <v>-89.5</v>
+      </c>
+      <c r="AQ2">
+        <v>-89.5</v>
       </c>
     </row>
     <row r="3">
@@ -686,7 +692,7 @@
         </is>
       </c>
       <c r="K3">
-        <v>-0.967</v>
+        <v>-0.921</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -710,61 +716,67 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>2.07</v>
+        <v>0.373</v>
       </c>
       <c r="V3">
-        <v>0.2165271966527196</v>
+        <v>0.02207100591715977</v>
       </c>
       <c r="W3">
-        <v>-6.320261437908496</v>
+        <v>-0.2285359801488834</v>
       </c>
       <c r="X3">
-        <v>0.0640769953380476</v>
+        <v>0.1226965148274022</v>
       </c>
       <c r="Y3">
-        <v>-6.384338433246544</v>
+        <v>-0.3512324949762856</v>
       </c>
       <c r="Z3">
         <v>0</v>
       </c>
       <c r="AA3">
-        <v>-18.57692307692308</v>
+        <v>-0.4566326530612244</v>
       </c>
       <c r="AB3">
-        <v>0.0640769953380476</v>
+        <v>0.121543332350794</v>
       </c>
       <c r="AC3">
-        <v>-18.64100007226113</v>
+        <v>-0.5781759854120184</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>0.372</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0</v>
+        <v>0.372</v>
       </c>
       <c r="AG3">
-        <v>-2.07</v>
+        <v>-0.001000000000000001</v>
       </c>
       <c r="AH3">
-        <v>0</v>
+        <v>0.02153774895785086</v>
       </c>
       <c r="AI3">
-        <v>0</v>
+        <v>0.07894736842105264</v>
       </c>
       <c r="AJ3">
-        <v>-0.2763684913217623</v>
+        <v>-5.917509911829108e-05</v>
       </c>
       <c r="AK3">
-        <v>-0.7064846416382251</v>
+        <v>-0.0002304678497349622</v>
       </c>
       <c r="AL3">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="AM3">
-        <v>0</v>
+        <v>0.01</v>
+      </c>
+      <c r="AO3">
+        <v>-89.5</v>
+      </c>
+      <c r="AQ3">
+        <v>-89.5</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/bermuda/bermuda_metals_mining.xlsx
+++ b/research/traditional_assets/database/data/bermuda/bermuda_metals_mining.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="K2">
-        <v>-0.921</v>
+        <v>-0.959</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -612,67 +612,67 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>0.373</v>
+        <v>0.284</v>
       </c>
       <c r="V2">
-        <v>0.02207100591715977</v>
+        <v>0.0142</v>
       </c>
       <c r="W2">
-        <v>-0.2285359801488834</v>
+        <v>-0.2845697329376854</v>
       </c>
       <c r="X2">
-        <v>0.1226965148274022</v>
+        <v>0.09779485433451426</v>
       </c>
       <c r="Y2">
-        <v>-0.3512324949762856</v>
+        <v>-0.3823645872721997</v>
       </c>
       <c r="Z2">
         <v>0</v>
       </c>
       <c r="AA2">
-        <v>-0.4566326530612244</v>
+        <v>-0.2341941228851291</v>
       </c>
       <c r="AB2">
-        <v>0.121543332350794</v>
+        <v>0.09687998883497667</v>
       </c>
       <c r="AC2">
-        <v>-0.5781759854120184</v>
+        <v>-0.3310741117201058</v>
       </c>
       <c r="AD2">
-        <v>0.372</v>
+        <v>0.536</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>0.372</v>
+        <v>0.536</v>
       </c>
       <c r="AG2">
-        <v>-0.001000000000000001</v>
+        <v>0.2520000000000001</v>
       </c>
       <c r="AH2">
-        <v>0.02153774895785086</v>
+        <v>0.02610050642773666</v>
       </c>
       <c r="AI2">
-        <v>0.07894736842105264</v>
+        <v>0.1053873377900118</v>
       </c>
       <c r="AJ2">
-        <v>-5.917509911829108e-05</v>
+        <v>0.01244321548489039</v>
       </c>
       <c r="AK2">
-        <v>-0.0002304678497349622</v>
+        <v>0.05247813411078719</v>
       </c>
       <c r="AL2">
-        <v>0.01</v>
+        <v>0.062</v>
       </c>
       <c r="AM2">
-        <v>0.01</v>
+        <v>0.062</v>
       </c>
       <c r="AO2">
-        <v>-89.5</v>
+        <v>-12.7258064516129</v>
       </c>
       <c r="AQ2">
-        <v>-89.5</v>
+        <v>-12.7258064516129</v>
       </c>
     </row>
     <row r="3">
@@ -692,7 +692,7 @@
         </is>
       </c>
       <c r="K3">
-        <v>-0.921</v>
+        <v>-0.959</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -716,67 +716,67 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0.373</v>
+        <v>0.284</v>
       </c>
       <c r="V3">
-        <v>0.02207100591715977</v>
+        <v>0.0142</v>
       </c>
       <c r="W3">
-        <v>-0.2285359801488834</v>
+        <v>-0.2845697329376854</v>
       </c>
       <c r="X3">
-        <v>0.1226965148274022</v>
+        <v>0.09779485433451426</v>
       </c>
       <c r="Y3">
-        <v>-0.3512324949762856</v>
+        <v>-0.3823645872721997</v>
       </c>
       <c r="Z3">
         <v>0</v>
       </c>
       <c r="AA3">
-        <v>-0.4566326530612244</v>
+        <v>-0.2341941228851291</v>
       </c>
       <c r="AB3">
-        <v>0.121543332350794</v>
+        <v>0.09687998883497667</v>
       </c>
       <c r="AC3">
-        <v>-0.5781759854120184</v>
+        <v>-0.3310741117201058</v>
       </c>
       <c r="AD3">
-        <v>0.372</v>
+        <v>0.536</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.372</v>
+        <v>0.536</v>
       </c>
       <c r="AG3">
-        <v>-0.001000000000000001</v>
+        <v>0.2520000000000001</v>
       </c>
       <c r="AH3">
-        <v>0.02153774895785086</v>
+        <v>0.02610050642773666</v>
       </c>
       <c r="AI3">
-        <v>0.07894736842105264</v>
+        <v>0.1053873377900118</v>
       </c>
       <c r="AJ3">
-        <v>-5.917509911829108e-05</v>
+        <v>0.01244321548489039</v>
       </c>
       <c r="AK3">
-        <v>-0.0002304678497349622</v>
+        <v>0.05247813411078719</v>
       </c>
       <c r="AL3">
-        <v>0.01</v>
+        <v>0.062</v>
       </c>
       <c r="AM3">
-        <v>0.01</v>
+        <v>0.062</v>
       </c>
       <c r="AO3">
-        <v>-89.5</v>
+        <v>-12.7258064516129</v>
       </c>
       <c r="AQ3">
-        <v>-89.5</v>
+        <v>-12.7258064516129</v>
       </c>
     </row>
   </sheetData>
